--- a/data/raw/metamethod review/master coding/codebook_scoring_master.xlsx
+++ b/data/raw/metamethod review/master coding/codebook_scoring_master.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10720"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/308fe5676bbb12c4/Documents/GitHub/igt-project/data/raw/metamethod review/master coding/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/akuelp/GitHub/igt-project/data/raw/metamethod review/master coding/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="11_8B923FC38F79A8D366075C52F37BD2724ACEA856" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D72EC37-BB8E-4516-AAEE-9E7D94514C0C}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F1A8F31-63BB-9F49-953B-6BF06F5D8563}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="76440" yWindow="4365" windowWidth="20265" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="60160" windowHeight="31940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1575,22 +1575,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:K807"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="12.1328125" customWidth="1"/>
-    <col min="5" max="5" width="81.3984375" customWidth="1"/>
-    <col min="6" max="6" width="20.265625" customWidth="1"/>
+    <col min="3" max="3" width="12.1640625" customWidth="1"/>
+    <col min="5" max="5" width="81.33203125" customWidth="1"/>
+    <col min="6" max="6" width="20.33203125" customWidth="1"/>
     <col min="7" max="7" width="25" customWidth="1"/>
-    <col min="8" max="8" width="17.265625" customWidth="1"/>
-    <col min="9" max="9" width="23.86328125" customWidth="1"/>
-    <col min="10" max="10" width="9.1328125" customWidth="1"/>
-    <col min="11" max="11" width="16.1328125" customWidth="1"/>
+    <col min="8" max="8" width="17.33203125" customWidth="1"/>
+    <col min="9" max="9" width="23.83203125" customWidth="1"/>
+    <col min="10" max="10" width="9.1640625" customWidth="1"/>
+    <col min="11" max="11" width="16.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1625,7 +1624,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>34</v>
       </c>
@@ -1660,7 +1659,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>35</v>
       </c>
@@ -1695,7 +1694,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>53</v>
       </c>
@@ -1730,7 +1729,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>127</v>
       </c>
@@ -1765,7 +1764,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>68</v>
       </c>
@@ -1800,7 +1799,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>64</v>
       </c>
@@ -1835,7 +1834,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>133</v>
       </c>
@@ -1870,7 +1869,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>6</v>
       </c>
@@ -1905,7 +1904,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>93</v>
       </c>
@@ -1940,7 +1939,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>12</v>
       </c>
@@ -1975,7 +1974,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>9</v>
       </c>
@@ -2010,7 +2009,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>8</v>
       </c>
@@ -2045,7 +2044,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>95</v>
       </c>
@@ -2080,7 +2079,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>116</v>
       </c>
@@ -2115,7 +2114,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>60</v>
       </c>
@@ -2150,7 +2149,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>127</v>
       </c>
@@ -2185,7 +2184,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>39</v>
       </c>
@@ -2220,7 +2219,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>26</v>
       </c>
@@ -2255,7 +2254,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>33</v>
       </c>
@@ -2290,7 +2289,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>33</v>
       </c>
@@ -2325,7 +2324,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>61</v>
       </c>
@@ -2360,7 +2359,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>61</v>
       </c>
@@ -2395,7 +2394,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>100</v>
       </c>
@@ -2430,7 +2429,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>6</v>
       </c>
@@ -2465,7 +2464,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>122</v>
       </c>
@@ -2500,7 +2499,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>93</v>
       </c>
@@ -2535,7 +2534,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>18</v>
       </c>
@@ -2570,7 +2569,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>136</v>
       </c>
@@ -2605,7 +2604,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>136</v>
       </c>
@@ -2640,7 +2639,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>19</v>
       </c>
@@ -2675,7 +2674,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>35</v>
       </c>
@@ -2710,7 +2709,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>43</v>
       </c>
@@ -2745,7 +2744,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>57</v>
       </c>
@@ -2780,7 +2779,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>61</v>
       </c>
@@ -2815,7 +2814,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>136</v>
       </c>
@@ -2850,7 +2849,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="37" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>18</v>
       </c>
@@ -2885,7 +2884,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>34</v>
       </c>
@@ -2920,7 +2919,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="39" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>34</v>
       </c>
@@ -2955,7 +2954,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="40" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>100</v>
       </c>
@@ -2990,7 +2989,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>100</v>
       </c>
@@ -3025,7 +3024,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="42" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>100</v>
       </c>
@@ -3060,7 +3059,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="43" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>100</v>
       </c>
@@ -3095,7 +3094,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="44" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>100</v>
       </c>
@@ -3130,7 +3129,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="45" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>100</v>
       </c>
@@ -3165,7 +3164,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="46" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>128</v>
       </c>
@@ -3200,7 +3199,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="47" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>101</v>
       </c>
@@ -3235,7 +3234,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="48" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>3</v>
       </c>
@@ -3270,7 +3269,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>43</v>
       </c>
@@ -3305,7 +3304,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>43</v>
       </c>
@@ -3340,7 +3339,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>43</v>
       </c>
@@ -3375,7 +3374,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="52" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>43</v>
       </c>
@@ -3410,7 +3409,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="53" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>138</v>
       </c>
@@ -3445,7 +3444,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="54" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>135</v>
       </c>
@@ -3480,7 +3479,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="55" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>135</v>
       </c>
@@ -3515,7 +3514,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="56" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>135</v>
       </c>
@@ -3550,7 +3549,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>135</v>
       </c>
@@ -3585,7 +3584,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>135</v>
       </c>
@@ -3620,7 +3619,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>135</v>
       </c>
@@ -3655,7 +3654,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>30</v>
       </c>
@@ -3690,7 +3689,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="61" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>19</v>
       </c>
@@ -3725,7 +3724,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="62" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>35</v>
       </c>
@@ -3760,7 +3759,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="63" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>43</v>
       </c>
@@ -3795,7 +3794,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="64" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>57</v>
       </c>
@@ -3830,7 +3829,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="65" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>61</v>
       </c>
@@ -3865,7 +3864,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="66" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>4</v>
       </c>
@@ -3900,7 +3899,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="67" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>12</v>
       </c>
@@ -3935,7 +3934,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="68" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>25</v>
       </c>
@@ -3970,7 +3969,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="69" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>34</v>
       </c>
@@ -4005,7 +4004,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="70" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>39</v>
       </c>
@@ -4040,7 +4039,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="71" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>53</v>
       </c>
@@ -4075,7 +4074,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="72" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>57</v>
       </c>
@@ -4110,7 +4109,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="73" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>59</v>
       </c>
@@ -4145,7 +4144,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="74" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>61</v>
       </c>
@@ -4180,7 +4179,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="75" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>75</v>
       </c>
@@ -4215,7 +4214,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="76" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>87</v>
       </c>
@@ -4250,7 +4249,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="77" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>89</v>
       </c>
@@ -4285,7 +4284,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="78" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>93</v>
       </c>
@@ -4320,7 +4319,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="79" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>100</v>
       </c>
@@ -4355,7 +4354,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="80" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>103</v>
       </c>
@@ -4390,7 +4389,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="81" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>103</v>
       </c>
@@ -4425,7 +4424,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="82" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>116</v>
       </c>
@@ -4460,7 +4459,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="83" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>117</v>
       </c>
@@ -4495,7 +4494,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="84" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>117</v>
       </c>
@@ -4530,7 +4529,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="85" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>47</v>
       </c>
@@ -4565,7 +4564,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="86" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>103</v>
       </c>
@@ -4600,7 +4599,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="87" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>103</v>
       </c>
@@ -4635,7 +4634,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="88" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>87</v>
       </c>
@@ -4670,7 +4669,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="89" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>18</v>
       </c>
@@ -4705,7 +4704,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="90" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>89</v>
       </c>
@@ -4740,7 +4739,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="91" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>117</v>
       </c>
@@ -4775,7 +4774,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="92" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>117</v>
       </c>
@@ -4810,7 +4809,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="93" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>103</v>
       </c>
@@ -4845,7 +4844,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="94" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>103</v>
       </c>
@@ -4880,7 +4879,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="95" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>87</v>
       </c>
@@ -4915,7 +4914,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="96" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>18</v>
       </c>
@@ -4950,7 +4949,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="97" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>89</v>
       </c>
@@ -4985,7 +4984,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="98" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>117</v>
       </c>
@@ -5020,7 +5019,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="99" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>47</v>
       </c>
@@ -5055,7 +5054,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="100" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>103</v>
       </c>
@@ -5090,7 +5089,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="101" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>103</v>
       </c>
@@ -5125,7 +5124,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="102" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>87</v>
       </c>
@@ -5160,7 +5159,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="103" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>18</v>
       </c>
@@ -5195,7 +5194,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="104" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>89</v>
       </c>
@@ -5230,7 +5229,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="105" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>117</v>
       </c>
@@ -5265,7 +5264,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="106" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>87</v>
       </c>
@@ -5300,7 +5299,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="107" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>18</v>
       </c>
@@ -5335,7 +5334,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="108" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>89</v>
       </c>
@@ -5370,7 +5369,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="109" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>117</v>
       </c>
@@ -5405,7 +5404,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="110" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>18</v>
       </c>
@@ -5440,7 +5439,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="111" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>89</v>
       </c>
@@ -5475,7 +5474,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="112" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>117</v>
       </c>
@@ -5510,7 +5509,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="113" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A113">
         <v>117</v>
       </c>
@@ -5545,7 +5544,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="114" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A114">
         <v>117</v>
       </c>
@@ -5580,7 +5579,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="115" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>117</v>
       </c>
@@ -5615,7 +5614,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="116" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A116">
         <v>12</v>
       </c>
@@ -5650,7 +5649,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="117" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A117">
         <v>4</v>
       </c>
@@ -5685,7 +5684,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="118" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A118">
         <v>9</v>
       </c>
@@ -5720,7 +5719,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="119" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>12</v>
       </c>
@@ -5755,7 +5754,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="120" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A120">
         <v>24</v>
       </c>
@@ -5790,7 +5789,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="121" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A121">
         <v>35</v>
       </c>
@@ -5825,7 +5824,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="122" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A122">
         <v>71</v>
       </c>
@@ -5860,7 +5859,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="123" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A123">
         <v>72</v>
       </c>
@@ -5895,7 +5894,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="124" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A124">
         <v>72</v>
       </c>
@@ -5930,7 +5929,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="125" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A125">
         <v>81</v>
       </c>
@@ -5965,7 +5964,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="126" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A126">
         <v>87</v>
       </c>
@@ -6000,7 +5999,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="127" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A127">
         <v>97</v>
       </c>
@@ -6035,7 +6034,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="128" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A128">
         <v>103</v>
       </c>
@@ -6070,7 +6069,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="129" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A129">
         <v>103</v>
       </c>
@@ -6105,7 +6104,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="130" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A130">
         <v>117</v>
       </c>
@@ -6140,7 +6139,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="131" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A131">
         <v>134</v>
       </c>
@@ -6175,7 +6174,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="132" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A132">
         <v>140</v>
       </c>
@@ -6210,7 +6209,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="133" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A133">
         <v>103</v>
       </c>
@@ -6245,7 +6244,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="134" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A134">
         <v>103</v>
       </c>
@@ -6280,7 +6279,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="135" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A135">
         <v>87</v>
       </c>
@@ -6315,7 +6314,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="136" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A136">
         <v>97</v>
       </c>
@@ -6350,7 +6349,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="137" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A137">
         <v>39</v>
       </c>
@@ -6385,7 +6384,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="138" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A138">
         <v>61</v>
       </c>
@@ -6420,7 +6419,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="139" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A139">
         <v>81</v>
       </c>
@@ -6455,7 +6454,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="140" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A140">
         <v>134</v>
       </c>
@@ -6490,7 +6489,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="141" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A141">
         <v>103</v>
       </c>
@@ -6525,7 +6524,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="142" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A142">
         <v>103</v>
       </c>
@@ -6560,7 +6559,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="143" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A143">
         <v>87</v>
       </c>
@@ -6595,7 +6594,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="144" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A144">
         <v>97</v>
       </c>
@@ -6630,7 +6629,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="145" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A145">
         <v>39</v>
       </c>
@@ -6665,7 +6664,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="146" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A146">
         <v>61</v>
       </c>
@@ -6700,7 +6699,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="147" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A147">
         <v>81</v>
       </c>
@@ -6735,7 +6734,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="148" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A148">
         <v>134</v>
       </c>
@@ -6770,7 +6769,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="149" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A149">
         <v>103</v>
       </c>
@@ -6805,7 +6804,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="150" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A150">
         <v>103</v>
       </c>
@@ -6840,7 +6839,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="151" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A151">
         <v>87</v>
       </c>
@@ -6875,7 +6874,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="152" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A152">
         <v>97</v>
       </c>
@@ -6910,7 +6909,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="153" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A153">
         <v>39</v>
       </c>
@@ -6945,7 +6944,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="154" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A154">
         <v>61</v>
       </c>
@@ -6980,7 +6979,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="155" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A155">
         <v>81</v>
       </c>
@@ -7015,7 +7014,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="156" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A156">
         <v>134</v>
       </c>
@@ -7050,7 +7049,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="157" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A157">
         <v>87</v>
       </c>
@@ -7085,7 +7084,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="158" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A158">
         <v>39</v>
       </c>
@@ -7120,7 +7119,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="159" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A159">
         <v>61</v>
       </c>
@@ -7155,7 +7154,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="160" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A160">
         <v>81</v>
       </c>
@@ -7190,7 +7189,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="161" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A161">
         <v>134</v>
       </c>
@@ -7225,7 +7224,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="162" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A162">
         <v>39</v>
       </c>
@@ -7260,7 +7259,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="163" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A163">
         <v>61</v>
       </c>
@@ -7295,7 +7294,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="164" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A164">
         <v>81</v>
       </c>
@@ -7330,7 +7329,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="165" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A165">
         <v>97</v>
       </c>
@@ -7365,7 +7364,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="166" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A166">
         <v>134</v>
       </c>
@@ -7400,7 +7399,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="167" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A167">
         <v>4</v>
       </c>
@@ -7435,7 +7434,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="168" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A168">
         <v>12</v>
       </c>
@@ -7470,7 +7469,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="169" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A169">
         <v>39</v>
       </c>
@@ -7505,7 +7504,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="170" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A170">
         <v>117</v>
       </c>
@@ -7540,7 +7539,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="171" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A171">
         <v>4</v>
       </c>
@@ -7575,7 +7574,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="172" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A172">
         <v>12</v>
       </c>
@@ -7610,7 +7609,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="173" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A173">
         <v>25</v>
       </c>
@@ -7645,7 +7644,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="174" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A174">
         <v>34</v>
       </c>
@@ -7680,7 +7679,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="175" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A175">
         <v>39</v>
       </c>
@@ -7715,7 +7714,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="176" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A176">
         <v>53</v>
       </c>
@@ -7750,7 +7749,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="177" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A177">
         <v>57</v>
       </c>
@@ -7785,7 +7784,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="178" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A178">
         <v>59</v>
       </c>
@@ -7820,7 +7819,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="179" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A179">
         <v>61</v>
       </c>
@@ -7855,7 +7854,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="180" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A180">
         <v>75</v>
       </c>
@@ -7890,7 +7889,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="181" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A181">
         <v>87</v>
       </c>
@@ -7925,7 +7924,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="182" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A182">
         <v>89</v>
       </c>
@@ -7960,7 +7959,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="183" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A183">
         <v>93</v>
       </c>
@@ -7995,7 +7994,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="184" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A184">
         <v>103</v>
       </c>
@@ -8030,7 +8029,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="185" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A185">
         <v>103</v>
       </c>
@@ -8065,7 +8064,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="186" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A186">
         <v>116</v>
       </c>
@@ -8100,7 +8099,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="187" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A187">
         <v>117</v>
       </c>
@@ -8135,7 +8134,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="188" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A188">
         <v>117</v>
       </c>
@@ -8170,7 +8169,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="189" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A189">
         <v>47</v>
       </c>
@@ -8205,7 +8204,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="190" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A190">
         <v>103</v>
       </c>
@@ -8240,7 +8239,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="191" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A191">
         <v>103</v>
       </c>
@@ -8275,7 +8274,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="192" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A192">
         <v>87</v>
       </c>
@@ -8310,7 +8309,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="193" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A193">
         <v>18</v>
       </c>
@@ -8345,7 +8344,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="194" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A194">
         <v>89</v>
       </c>
@@ -8380,7 +8379,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="195" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="195" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A195">
         <v>117</v>
       </c>
@@ -8415,7 +8414,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="196" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="196" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A196">
         <v>117</v>
       </c>
@@ -8450,7 +8449,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="197" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="197" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A197">
         <v>103</v>
       </c>
@@ -8485,7 +8484,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="198" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="198" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A198">
         <v>103</v>
       </c>
@@ -8520,7 +8519,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="199" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A199">
         <v>87</v>
       </c>
@@ -8555,7 +8554,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="200" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A200">
         <v>18</v>
       </c>
@@ -8590,7 +8589,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="201" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A201">
         <v>89</v>
       </c>
@@ -8625,7 +8624,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="202" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="202" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A202">
         <v>117</v>
       </c>
@@ -8660,7 +8659,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="203" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="203" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A203">
         <v>47</v>
       </c>
@@ -8695,7 +8694,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="204" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="204" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A204">
         <v>103</v>
       </c>
@@ -8730,7 +8729,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="205" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="205" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A205">
         <v>103</v>
       </c>
@@ -8765,7 +8764,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="206" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="206" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A206">
         <v>87</v>
       </c>
@@ -8800,7 +8799,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="207" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="207" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A207">
         <v>18</v>
       </c>
@@ -8835,7 +8834,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="208" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="208" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A208">
         <v>89</v>
       </c>
@@ -8870,7 +8869,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="209" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="209" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A209">
         <v>117</v>
       </c>
@@ -8905,7 +8904,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="210" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="210" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A210">
         <v>87</v>
       </c>
@@ -8940,7 +8939,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="211" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="211" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A211">
         <v>18</v>
       </c>
@@ -8975,7 +8974,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="212" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="212" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A212">
         <v>89</v>
       </c>
@@ -9010,7 +9009,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="213" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="213" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A213">
         <v>117</v>
       </c>
@@ -9045,7 +9044,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="214" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="214" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A214">
         <v>18</v>
       </c>
@@ -9080,7 +9079,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="215" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="215" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A215">
         <v>89</v>
       </c>
@@ -9115,7 +9114,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="216" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="216" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A216">
         <v>117</v>
       </c>
@@ -9150,7 +9149,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="217" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="217" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A217">
         <v>117</v>
       </c>
@@ -9185,7 +9184,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="218" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="218" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A218">
         <v>117</v>
       </c>
@@ -9220,7 +9219,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="219" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="219" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A219">
         <v>117</v>
       </c>
@@ -9255,7 +9254,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="220" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="220" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A220">
         <v>4</v>
       </c>
@@ -9290,7 +9289,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="221" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="221" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A221">
         <v>12</v>
       </c>
@@ -9325,7 +9324,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="222" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="222" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A222">
         <v>25</v>
       </c>
@@ -9360,7 +9359,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="223" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="223" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A223">
         <v>34</v>
       </c>
@@ -9395,7 +9394,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="224" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="224" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A224">
         <v>39</v>
       </c>
@@ -9430,7 +9429,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="225" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="225" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A225">
         <v>53</v>
       </c>
@@ -9465,7 +9464,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="226" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="226" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A226">
         <v>57</v>
       </c>
@@ -9500,7 +9499,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="227" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="227" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A227">
         <v>59</v>
       </c>
@@ -9535,7 +9534,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="228" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="228" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A228">
         <v>61</v>
       </c>
@@ -9570,7 +9569,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="229" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="229" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A229">
         <v>75</v>
       </c>
@@ -9605,7 +9604,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="230" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="230" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A230">
         <v>87</v>
       </c>
@@ -9640,7 +9639,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="231" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="231" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A231">
         <v>93</v>
       </c>
@@ -9675,7 +9674,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="232" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="232" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A232">
         <v>103</v>
       </c>
@@ -9710,7 +9709,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="233" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="233" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A233">
         <v>103</v>
       </c>
@@ -9745,7 +9744,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="234" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="234" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A234">
         <v>116</v>
       </c>
@@ -9780,7 +9779,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="235" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="235" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A235">
         <v>117</v>
       </c>
@@ -9815,7 +9814,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="236" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="236" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A236">
         <v>117</v>
       </c>
@@ -9850,7 +9849,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="237" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="237" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A237">
         <v>47</v>
       </c>
@@ -9885,7 +9884,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="238" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="238" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A238">
         <v>103</v>
       </c>
@@ -9920,7 +9919,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="239" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="239" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A239">
         <v>103</v>
       </c>
@@ -9955,7 +9954,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="240" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="240" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A240">
         <v>87</v>
       </c>
@@ -9990,7 +9989,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="241" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="241" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A241">
         <v>18</v>
       </c>
@@ -10025,7 +10024,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="242" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="242" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A242">
         <v>89</v>
       </c>
@@ -10060,7 +10059,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="243" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="243" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A243">
         <v>117</v>
       </c>
@@ -10095,7 +10094,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="244" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="244" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A244">
         <v>117</v>
       </c>
@@ -10130,7 +10129,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="245" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="245" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A245">
         <v>103</v>
       </c>
@@ -10165,7 +10164,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="246" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="246" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A246">
         <v>103</v>
       </c>
@@ -10200,7 +10199,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="247" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="247" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A247">
         <v>87</v>
       </c>
@@ -10235,7 +10234,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="248" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="248" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A248">
         <v>18</v>
       </c>
@@ -10270,7 +10269,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="249" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="249" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A249">
         <v>89</v>
       </c>
@@ -10305,7 +10304,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="250" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="250" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A250">
         <v>117</v>
       </c>
@@ -10340,7 +10339,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="251" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="251" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A251">
         <v>47</v>
       </c>
@@ -10375,7 +10374,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="252" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="252" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A252">
         <v>103</v>
       </c>
@@ -10410,7 +10409,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="253" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="253" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A253">
         <v>103</v>
       </c>
@@ -10445,7 +10444,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="254" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="254" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A254">
         <v>87</v>
       </c>
@@ -10480,7 +10479,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="255" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="255" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A255">
         <v>18</v>
       </c>
@@ -10515,7 +10514,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="256" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="256" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A256">
         <v>89</v>
       </c>
@@ -10550,7 +10549,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="257" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="257" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A257">
         <v>117</v>
       </c>
@@ -10585,7 +10584,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="258" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="258" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A258">
         <v>87</v>
       </c>
@@ -10620,7 +10619,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="259" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="259" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A259">
         <v>18</v>
       </c>
@@ -10655,7 +10654,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="260" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="260" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A260">
         <v>89</v>
       </c>
@@ -10690,7 +10689,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="261" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="261" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A261">
         <v>117</v>
       </c>
@@ -10725,7 +10724,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="262" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="262" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A262">
         <v>18</v>
       </c>
@@ -10760,7 +10759,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="263" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="263" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A263">
         <v>89</v>
       </c>
@@ -10795,7 +10794,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="264" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="264" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A264">
         <v>117</v>
       </c>
@@ -10830,7 +10829,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="265" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="265" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A265">
         <v>117</v>
       </c>
@@ -10865,7 +10864,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="266" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="266" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A266">
         <v>117</v>
       </c>
@@ -10900,7 +10899,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="267" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="267" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A267">
         <v>117</v>
       </c>
@@ -10935,7 +10934,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="268" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="268" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A268">
         <v>4</v>
       </c>
@@ -10970,7 +10969,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="269" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="269" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A269">
         <v>12</v>
       </c>
@@ -11005,7 +11004,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="270" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="270" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A270">
         <v>18</v>
       </c>
@@ -11040,7 +11039,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="271" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="271" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A271">
         <v>24</v>
       </c>
@@ -11075,7 +11074,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="272" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="272" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A272">
         <v>35</v>
       </c>
@@ -11110,7 +11109,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="273" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="273" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A273">
         <v>36</v>
       </c>
@@ -11145,7 +11144,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="274" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="274" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A274">
         <v>37</v>
       </c>
@@ -11180,7 +11179,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="275" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="275" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A275">
         <v>51</v>
       </c>
@@ -11215,7 +11214,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="276" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="276" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A276">
         <v>70</v>
       </c>
@@ -11250,7 +11249,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="277" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="277" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A277">
         <v>81</v>
       </c>
@@ -11285,7 +11284,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="278" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="278" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A278">
         <v>87</v>
       </c>
@@ -11320,7 +11319,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="279" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="279" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A279">
         <v>95</v>
       </c>
@@ -11355,7 +11354,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="280" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="280" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A280">
         <v>97</v>
       </c>
@@ -11390,7 +11389,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="281" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="281" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A281">
         <v>98</v>
       </c>
@@ -11425,7 +11424,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="282" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="282" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A282">
         <v>103</v>
       </c>
@@ -11460,7 +11459,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="283" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="283" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A283">
         <v>103</v>
       </c>
@@ -11495,7 +11494,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="284" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="284" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A284">
         <v>117</v>
       </c>
@@ -11530,7 +11529,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="285" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="285" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A285">
         <v>136</v>
       </c>
@@ -11565,7 +11564,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="286" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="286" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A286">
         <v>139</v>
       </c>
@@ -11600,7 +11599,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="287" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="287" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A287">
         <v>18</v>
       </c>
@@ -11635,7 +11634,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="288" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="288" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A288">
         <v>20</v>
       </c>
@@ -11670,7 +11669,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="289" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="289" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A289">
         <v>87</v>
       </c>
@@ -11705,7 +11704,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="290" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="290" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A290">
         <v>136</v>
       </c>
@@ -11740,7 +11739,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="291" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="291" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A291">
         <v>97</v>
       </c>
@@ -11775,7 +11774,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="292" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="292" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A292">
         <v>39</v>
       </c>
@@ -11810,7 +11809,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="293" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="293" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A293">
         <v>74</v>
       </c>
@@ -11845,7 +11844,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="294" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="294" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A294">
         <v>81</v>
       </c>
@@ -11880,7 +11879,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="295" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="295" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A295">
         <v>95</v>
       </c>
@@ -11915,7 +11914,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="296" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="296" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A296">
         <v>139</v>
       </c>
@@ -11950,7 +11949,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="297" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="297" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A297">
         <v>139</v>
       </c>
@@ -11985,7 +11984,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="298" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="298" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A298">
         <v>20</v>
       </c>
@@ -12020,7 +12019,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="299" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="299" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A299">
         <v>87</v>
       </c>
@@ -12055,7 +12054,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="300" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="300" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A300">
         <v>136</v>
       </c>
@@ -12090,7 +12089,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="301" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="301" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A301">
         <v>97</v>
       </c>
@@ -12125,7 +12124,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="302" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="302" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A302">
         <v>39</v>
       </c>
@@ -12160,7 +12159,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="303" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="303" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A303">
         <v>74</v>
       </c>
@@ -12195,7 +12194,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="304" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="304" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A304">
         <v>81</v>
       </c>
@@ -12230,7 +12229,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="305" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="305" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A305">
         <v>95</v>
       </c>
@@ -12265,7 +12264,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="306" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="306" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A306">
         <v>20</v>
       </c>
@@ -12300,7 +12299,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="307" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="307" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A307">
         <v>87</v>
       </c>
@@ -12335,7 +12334,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="308" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="308" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A308">
         <v>136</v>
       </c>
@@ -12370,7 +12369,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="309" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="309" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A309">
         <v>97</v>
       </c>
@@ -12405,7 +12404,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="310" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="310" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A310">
         <v>39</v>
       </c>
@@ -12440,7 +12439,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="311" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="311" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A311">
         <v>74</v>
       </c>
@@ -12475,7 +12474,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="312" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="312" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A312">
         <v>81</v>
       </c>
@@ -12510,7 +12509,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="313" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="313" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A313">
         <v>95</v>
       </c>
@@ -12545,7 +12544,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="314" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="314" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A314">
         <v>139</v>
       </c>
@@ -12580,7 +12579,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="315" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="315" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A315">
         <v>20</v>
       </c>
@@ -12615,7 +12614,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="316" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="316" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A316">
         <v>87</v>
       </c>
@@ -12650,7 +12649,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="317" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="317" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A317">
         <v>136</v>
       </c>
@@ -12685,7 +12684,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="318" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="318" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A318">
         <v>39</v>
       </c>
@@ -12720,7 +12719,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="319" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="319" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A319">
         <v>74</v>
       </c>
@@ -12755,7 +12754,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="320" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="320" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A320">
         <v>81</v>
       </c>
@@ -12790,7 +12789,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="321" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="321" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A321">
         <v>95</v>
       </c>
@@ -12825,7 +12824,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="322" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="322" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A322">
         <v>139</v>
       </c>
@@ -12860,7 +12859,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="323" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="323" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A323">
         <v>39</v>
       </c>
@@ -12895,7 +12894,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="324" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="324" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A324">
         <v>74</v>
       </c>
@@ -12930,7 +12929,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="325" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="325" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A325">
         <v>81</v>
       </c>
@@ -12965,7 +12964,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="326" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="326" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A326">
         <v>95</v>
       </c>
@@ -13000,7 +12999,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="327" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="327" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A327">
         <v>97</v>
       </c>
@@ -13035,7 +13034,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="328" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="328" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A328">
         <v>139</v>
       </c>
@@ -13070,7 +13069,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="329" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="329" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A329">
         <v>139</v>
       </c>
@@ -13105,7 +13104,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="330" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="330" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A330">
         <v>37</v>
       </c>
@@ -13140,7 +13139,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="331" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="331" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A331">
         <v>115</v>
       </c>
@@ -13175,7 +13174,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="332" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="332" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A332">
         <v>93</v>
       </c>
@@ -13210,7 +13209,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="333" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="333" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A333">
         <v>4</v>
       </c>
@@ -13245,7 +13244,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="334" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="334" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A334">
         <v>12</v>
       </c>
@@ -13280,7 +13279,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="335" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="335" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A335">
         <v>25</v>
       </c>
@@ -13315,7 +13314,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="336" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="336" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A336">
         <v>34</v>
       </c>
@@ -13350,7 +13349,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="337" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="337" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A337">
         <v>39</v>
       </c>
@@ -13385,7 +13384,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="338" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="338" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A338">
         <v>53</v>
       </c>
@@ -13420,7 +13419,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="339" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="339" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A339">
         <v>57</v>
       </c>
@@ -13455,7 +13454,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="340" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="340" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A340">
         <v>59</v>
       </c>
@@ -13490,7 +13489,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="341" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="341" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A341">
         <v>61</v>
       </c>
@@ -13525,7 +13524,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="342" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="342" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A342">
         <v>75</v>
       </c>
@@ -13560,7 +13559,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="343" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="343" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A343">
         <v>87</v>
       </c>
@@ -13595,7 +13594,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="344" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="344" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A344">
         <v>93</v>
       </c>
@@ -13630,7 +13629,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="345" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="345" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A345">
         <v>100</v>
       </c>
@@ -13665,7 +13664,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="346" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="346" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A346">
         <v>103</v>
       </c>
@@ -13700,7 +13699,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="347" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="347" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A347">
         <v>103</v>
       </c>
@@ -13735,7 +13734,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="348" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="348" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A348">
         <v>116</v>
       </c>
@@ -13770,7 +13769,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="349" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="349" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A349">
         <v>117</v>
       </c>
@@ -13805,7 +13804,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="350" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="350" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A350">
         <v>117</v>
       </c>
@@ -13840,7 +13839,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="351" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="351" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A351">
         <v>47</v>
       </c>
@@ -13875,7 +13874,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="352" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="352" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A352">
         <v>103</v>
       </c>
@@ -13910,7 +13909,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="353" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="353" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A353">
         <v>103</v>
       </c>
@@ -13945,7 +13944,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="354" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="354" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A354">
         <v>87</v>
       </c>
@@ -13980,7 +13979,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="355" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="355" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A355">
         <v>18</v>
       </c>
@@ -14015,7 +14014,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="356" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="356" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A356">
         <v>89</v>
       </c>
@@ -14050,7 +14049,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="357" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="357" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A357">
         <v>117</v>
       </c>
@@ -14085,7 +14084,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="358" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="358" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A358">
         <v>117</v>
       </c>
@@ -14120,7 +14119,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="359" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="359" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A359">
         <v>103</v>
       </c>
@@ -14155,7 +14154,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="360" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="360" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A360">
         <v>103</v>
       </c>
@@ -14190,7 +14189,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="361" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="361" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A361">
         <v>87</v>
       </c>
@@ -14225,7 +14224,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="362" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="362" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A362">
         <v>18</v>
       </c>
@@ -14260,7 +14259,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="363" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="363" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A363">
         <v>89</v>
       </c>
@@ -14295,7 +14294,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="364" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="364" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A364">
         <v>117</v>
       </c>
@@ -14330,7 +14329,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="365" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="365" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A365">
         <v>47</v>
       </c>
@@ -14365,7 +14364,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="366" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="366" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A366">
         <v>103</v>
       </c>
@@ -14400,7 +14399,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="367" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="367" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A367">
         <v>103</v>
       </c>
@@ -14435,7 +14434,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="368" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="368" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A368">
         <v>87</v>
       </c>
@@ -14470,7 +14469,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="369" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="369" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A369">
         <v>18</v>
       </c>
@@ -14505,7 +14504,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="370" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="370" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A370">
         <v>89</v>
       </c>
@@ -14540,7 +14539,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="371" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="371" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A371">
         <v>117</v>
       </c>
@@ -14575,7 +14574,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="372" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="372" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A372">
         <v>87</v>
       </c>
@@ -14610,7 +14609,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="373" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="373" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A373">
         <v>18</v>
       </c>
@@ -14645,7 +14644,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="374" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="374" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A374">
         <v>89</v>
       </c>
@@ -14680,7 +14679,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="375" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="375" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A375">
         <v>117</v>
       </c>
@@ -14715,7 +14714,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="376" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="376" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A376">
         <v>18</v>
       </c>
@@ -14750,7 +14749,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="377" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="377" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A377">
         <v>89</v>
       </c>
@@ -14785,7 +14784,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="378" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="378" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A378">
         <v>117</v>
       </c>
@@ -14820,7 +14819,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="379" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="379" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A379">
         <v>117</v>
       </c>
@@ -14855,7 +14854,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="380" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="380" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A380">
         <v>117</v>
       </c>
@@ -14890,7 +14889,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="381" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="381" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A381">
         <v>117</v>
       </c>
@@ -14925,7 +14924,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="382" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="382" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A382">
         <v>93</v>
       </c>
@@ -14960,7 +14959,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="383" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="383" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A383">
         <v>116</v>
       </c>
@@ -14995,7 +14994,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="384" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="384" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A384">
         <v>3</v>
       </c>
@@ -15030,7 +15029,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="385" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="385" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A385">
         <v>4</v>
       </c>
@@ -15065,7 +15064,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="386" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="386" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A386">
         <v>5</v>
       </c>
@@ -15100,7 +15099,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="387" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="387" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A387">
         <v>8</v>
       </c>
@@ -15135,7 +15134,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="388" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="388" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A388">
         <v>10</v>
       </c>
@@ -15170,7 +15169,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="389" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="389" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A389">
         <v>16</v>
       </c>
@@ -15205,7 +15204,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="390" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="390" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A390">
         <v>17</v>
       </c>
@@ -15240,7 +15239,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="391" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="391" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A391">
         <v>21</v>
       </c>
@@ -15275,7 +15274,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="392" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="392" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A392">
         <v>25</v>
       </c>
@@ -15310,7 +15309,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="393" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="393" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A393">
         <v>27</v>
       </c>
@@ -15345,7 +15344,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="394" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="394" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A394">
         <v>32</v>
       </c>
@@ -15380,7 +15379,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="395" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="395" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A395">
         <v>34</v>
       </c>
@@ -15415,7 +15414,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="396" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="396" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A396">
         <v>38</v>
       </c>
@@ -15450,7 +15449,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="397" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="397" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A397">
         <v>43</v>
       </c>
@@ -15485,7 +15484,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="398" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="398" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A398">
         <v>48</v>
       </c>
@@ -15520,7 +15519,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="399" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="399" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A399">
         <v>49</v>
       </c>
@@ -15555,7 +15554,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="400" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="400" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A400">
         <v>50</v>
       </c>
@@ -15590,7 +15589,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="401" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="401" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A401">
         <v>52</v>
       </c>
@@ -15625,7 +15624,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="402" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="402" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A402">
         <v>53</v>
       </c>
@@ -15660,7 +15659,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="403" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="403" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A403">
         <v>56</v>
       </c>
@@ -15695,7 +15694,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="404" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="404" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A404">
         <v>59</v>
       </c>
@@ -15730,7 +15729,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="405" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="405" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A405">
         <v>61</v>
       </c>
@@ -15765,7 +15764,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="406" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="406" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A406">
         <v>62</v>
       </c>
@@ -15800,7 +15799,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="407" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="407" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A407">
         <v>64</v>
       </c>
@@ -15835,7 +15834,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="408" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="408" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A408">
         <v>65</v>
       </c>
@@ -15870,7 +15869,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="409" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="409" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A409">
         <v>67</v>
       </c>
@@ -15905,7 +15904,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="410" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="410" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A410">
         <v>71</v>
       </c>
@@ -15940,7 +15939,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="411" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="411" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A411">
         <v>71</v>
       </c>
@@ -15975,7 +15974,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="412" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="412" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A412">
         <v>75</v>
       </c>
@@ -16010,7 +16009,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="413" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="413" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A413">
         <v>79</v>
       </c>
@@ -16045,7 +16044,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="414" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="414" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A414">
         <v>83</v>
       </c>
@@ -16080,7 +16079,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="415" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="415" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A415">
         <v>84</v>
       </c>
@@ -16115,7 +16114,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="416" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="416" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A416">
         <v>84</v>
       </c>
@@ -16150,7 +16149,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="417" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="417" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A417">
         <v>85</v>
       </c>
@@ -16185,7 +16184,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="418" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="418" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A418">
         <v>86</v>
       </c>
@@ -16220,7 +16219,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="419" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="419" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A419">
         <v>86</v>
       </c>
@@ -16255,7 +16254,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="420" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="420" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A420">
         <v>88</v>
       </c>
@@ -16290,7 +16289,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="421" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="421" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A421">
         <v>89</v>
       </c>
@@ -16325,7 +16324,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="422" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="422" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A422">
         <v>90</v>
       </c>
@@ -16360,7 +16359,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="423" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="423" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A423">
         <v>91</v>
       </c>
@@ -16395,7 +16394,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="424" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="424" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A424">
         <v>92</v>
       </c>
@@ -16430,7 +16429,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="425" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="425" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A425">
         <v>105</v>
       </c>
@@ -16465,7 +16464,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="426" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="426" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A426">
         <v>107</v>
       </c>
@@ -16500,7 +16499,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="427" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="427" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A427">
         <v>113</v>
       </c>
@@ -16535,7 +16534,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="428" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="428" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A428">
         <v>120</v>
       </c>
@@ -16570,7 +16569,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="429" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="429" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A429">
         <v>121</v>
       </c>
@@ -16605,7 +16604,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="430" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="430" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A430">
         <v>124</v>
       </c>
@@ -16640,7 +16639,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="431" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="431" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A431">
         <v>126</v>
       </c>
@@ -16675,7 +16674,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="432" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="432" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A432">
         <v>127</v>
       </c>
@@ -16710,7 +16709,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="433" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="433" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A433">
         <v>130</v>
       </c>
@@ -16745,7 +16744,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="434" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="434" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A434">
         <v>132</v>
       </c>
@@ -16780,7 +16779,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="435" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="435" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A435">
         <v>138</v>
       </c>
@@ -16815,7 +16814,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="436" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="436" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A436">
         <v>115</v>
       </c>
@@ -16850,7 +16849,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="437" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="437" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A437">
         <v>107</v>
       </c>
@@ -16885,7 +16884,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="438" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="438" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A438">
         <v>47</v>
       </c>
@@ -16920,7 +16919,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="439" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="439" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A439">
         <v>3</v>
       </c>
@@ -16955,7 +16954,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="440" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="440" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A440">
         <v>4</v>
       </c>
@@ -16990,7 +16989,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="441" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="441" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A441">
         <v>12</v>
       </c>
@@ -17025,7 +17024,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="442" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="442" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A442">
         <v>16</v>
       </c>
@@ -17060,7 +17059,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="443" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="443" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A443">
         <v>21</v>
       </c>
@@ -17095,7 +17094,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="444" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="444" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A444">
         <v>25</v>
       </c>
@@ -17130,7 +17129,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="445" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="445" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A445">
         <v>27</v>
       </c>
@@ -17165,7 +17164,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="446" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="446" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A446">
         <v>28</v>
       </c>
@@ -17200,7 +17199,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="447" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="447" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A447">
         <v>30</v>
       </c>
@@ -17235,7 +17234,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="448" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="448" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A448">
         <v>30</v>
       </c>
@@ -17270,7 +17269,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="449" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="449" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A449">
         <v>32</v>
       </c>
@@ -17305,7 +17304,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="450" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="450" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A450">
         <v>34</v>
       </c>
@@ -17340,7 +17339,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="451" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="451" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A451">
         <v>38</v>
       </c>
@@ -17375,7 +17374,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="452" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="452" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A452">
         <v>43</v>
       </c>
@@ -17410,7 +17409,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="453" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="453" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A453">
         <v>49</v>
       </c>
@@ -17445,7 +17444,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="454" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="454" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A454">
         <v>50</v>
       </c>
@@ -17480,7 +17479,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="455" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="455" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A455">
         <v>51</v>
       </c>
@@ -17515,7 +17514,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="456" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="456" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A456">
         <v>52</v>
       </c>
@@ -17550,7 +17549,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="457" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="457" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A457">
         <v>53</v>
       </c>
@@ -17585,7 +17584,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="458" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="458" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A458">
         <v>54</v>
       </c>
@@ -17620,7 +17619,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="459" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="459" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A459">
         <v>56</v>
       </c>
@@ -17655,7 +17654,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="460" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="460" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A460">
         <v>57</v>
       </c>
@@ -17690,7 +17689,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="461" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="461" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A461">
         <v>61</v>
       </c>
@@ -17725,7 +17724,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="462" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="462" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A462">
         <v>64</v>
       </c>
@@ -17760,7 +17759,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="463" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="463" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A463">
         <v>65</v>
       </c>
@@ -17795,7 +17794,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="464" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="464" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A464">
         <v>67</v>
       </c>
@@ -17830,7 +17829,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="465" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="465" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A465">
         <v>71</v>
       </c>
@@ -17865,7 +17864,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="466" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="466" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A466">
         <v>71</v>
       </c>
@@ -17900,7 +17899,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="467" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="467" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A467">
         <v>75</v>
       </c>
@@ -17935,7 +17934,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="468" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="468" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A468">
         <v>78</v>
       </c>
@@ -17970,7 +17969,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="469" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="469" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A469">
         <v>79</v>
       </c>
@@ -18005,7 +18004,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="470" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="470" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A470">
         <v>83</v>
       </c>
@@ -18040,7 +18039,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="471" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="471" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A471">
         <v>85</v>
       </c>
@@ -18075,7 +18074,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="472" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="472" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A472">
         <v>88</v>
       </c>
@@ -18110,7 +18109,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="473" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="473" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A473">
         <v>89</v>
       </c>
@@ -18145,7 +18144,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="474" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="474" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A474">
         <v>91</v>
       </c>
@@ -18180,7 +18179,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="475" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="475" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A475">
         <v>96</v>
       </c>
@@ -18215,7 +18214,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="476" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="476" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A476">
         <v>96</v>
       </c>
@@ -18250,7 +18249,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="477" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="477" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A477">
         <v>101</v>
       </c>
@@ -18285,7 +18284,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="478" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="478" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A478">
         <v>105</v>
       </c>
@@ -18320,7 +18319,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="479" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="479" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A479">
         <v>113</v>
       </c>
@@ -18355,7 +18354,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="480" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="480" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A480">
         <v>121</v>
       </c>
@@ -18390,7 +18389,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="481" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="481" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A481">
         <v>124</v>
       </c>
@@ -18425,7 +18424,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="482" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="482" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A482">
         <v>127</v>
       </c>
@@ -18460,7 +18459,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="483" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="483" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A483">
         <v>128</v>
       </c>
@@ -18495,7 +18494,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="484" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="484" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A484">
         <v>130</v>
       </c>
@@ -18530,7 +18529,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="485" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="485" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A485">
         <v>131</v>
       </c>
@@ -18565,7 +18564,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="486" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="486" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A486">
         <v>132</v>
       </c>
@@ -18600,7 +18599,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="487" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="487" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A487">
         <v>133</v>
       </c>
@@ -18635,7 +18634,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="488" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="488" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A488">
         <v>134</v>
       </c>
@@ -18670,7 +18669,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="489" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="489" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A489">
         <v>137</v>
       </c>
@@ -18705,7 +18704,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="490" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="490" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A490">
         <v>138</v>
       </c>
@@ -18740,7 +18739,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="491" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="491" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A491">
         <v>115</v>
       </c>
@@ -18775,7 +18774,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="492" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="492" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A492">
         <v>115</v>
       </c>
@@ -18810,7 +18809,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="493" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="493" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A493">
         <v>115</v>
       </c>
@@ -18845,7 +18844,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="494" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="494" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A494">
         <v>115</v>
       </c>
@@ -18880,7 +18879,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="495" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="495" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A495">
         <v>115</v>
       </c>
@@ -18915,7 +18914,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="496" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="496" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A496">
         <v>115</v>
       </c>
@@ -18950,7 +18949,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="497" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="497" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A497">
         <v>115</v>
       </c>
@@ -18985,7 +18984,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="498" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="498" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A498">
         <v>115</v>
       </c>
@@ -19020,7 +19019,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="499" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="499" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A499">
         <v>115</v>
       </c>
@@ -19055,7 +19054,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="500" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="500" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A500">
         <v>115</v>
       </c>
@@ -19090,7 +19089,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="501" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="501" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A501">
         <v>115</v>
       </c>
@@ -19125,7 +19124,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="502" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="502" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A502">
         <v>107</v>
       </c>
@@ -19160,7 +19159,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="503" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="503" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A503">
         <v>3</v>
       </c>
@@ -19195,7 +19194,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="504" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="504" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A504">
         <v>4</v>
       </c>
@@ -19230,7 +19229,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="505" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="505" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A505">
         <v>12</v>
       </c>
@@ -19265,7 +19264,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="506" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="506" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A506">
         <v>16</v>
       </c>
@@ -19300,7 +19299,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="507" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="507" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A507">
         <v>21</v>
       </c>
@@ -19335,7 +19334,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="508" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="508" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A508">
         <v>25</v>
       </c>
@@ -19370,7 +19369,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="509" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="509" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A509">
         <v>27</v>
       </c>
@@ -19405,7 +19404,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="510" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="510" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A510">
         <v>28</v>
       </c>
@@ -19440,7 +19439,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="511" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="511" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A511">
         <v>30</v>
       </c>
@@ -19475,7 +19474,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="512" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="512" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A512">
         <v>30</v>
       </c>
@@ -19510,7 +19509,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="513" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="513" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A513">
         <v>32</v>
       </c>
@@ -19545,7 +19544,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="514" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="514" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A514">
         <v>34</v>
       </c>
@@ -19580,7 +19579,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="515" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="515" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A515">
         <v>38</v>
       </c>
@@ -19615,7 +19614,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="516" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="516" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A516">
         <v>43</v>
       </c>
@@ -19650,7 +19649,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="517" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="517" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A517">
         <v>49</v>
       </c>
@@ -19685,7 +19684,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="518" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="518" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A518">
         <v>50</v>
       </c>
@@ -19720,7 +19719,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="519" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="519" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A519">
         <v>51</v>
       </c>
@@ -19755,7 +19754,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="520" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="520" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A520">
         <v>52</v>
       </c>
@@ -19790,7 +19789,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="521" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="521" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A521">
         <v>53</v>
       </c>
@@ -19825,7 +19824,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="522" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="522" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A522">
         <v>54</v>
       </c>
@@ -19860,7 +19859,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="523" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="523" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A523">
         <v>56</v>
       </c>
@@ -19895,7 +19894,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="524" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="524" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A524">
         <v>57</v>
       </c>
@@ -19930,7 +19929,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="525" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="525" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A525">
         <v>61</v>
       </c>
@@ -19965,7 +19964,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="526" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="526" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A526">
         <v>64</v>
       </c>
@@ -20000,7 +19999,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="527" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="527" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A527">
         <v>65</v>
       </c>
@@ -20035,7 +20034,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="528" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="528" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A528">
         <v>67</v>
       </c>
@@ -20070,7 +20069,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="529" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="529" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A529">
         <v>71</v>
       </c>
@@ -20105,7 +20104,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="530" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="530" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A530">
         <v>71</v>
       </c>
@@ -20140,7 +20139,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="531" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="531" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A531">
         <v>75</v>
       </c>
@@ -20175,7 +20174,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="532" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="532" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A532">
         <v>78</v>
       </c>
@@ -20210,7 +20209,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="533" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="533" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A533">
         <v>79</v>
       </c>
@@ -20245,7 +20244,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="534" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="534" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A534">
         <v>83</v>
       </c>
@@ -20280,7 +20279,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="535" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="535" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A535">
         <v>85</v>
       </c>
@@ -20315,7 +20314,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="536" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="536" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A536">
         <v>88</v>
       </c>
@@ -20350,7 +20349,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="537" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="537" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A537">
         <v>89</v>
       </c>
@@ -20385,7 +20384,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="538" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="538" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A538">
         <v>91</v>
       </c>
@@ -20420,7 +20419,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="539" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="539" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A539">
         <v>96</v>
       </c>
@@ -20455,7 +20454,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="540" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="540" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A540">
         <v>96</v>
       </c>
@@ -20490,7 +20489,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="541" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="541" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A541">
         <v>101</v>
       </c>
@@ -20525,7 +20524,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="542" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="542" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A542">
         <v>105</v>
       </c>
@@ -20560,7 +20559,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="543" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="543" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A543">
         <v>113</v>
       </c>
@@ -20595,7 +20594,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="544" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="544" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A544">
         <v>121</v>
       </c>
@@ -20630,7 +20629,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="545" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="545" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A545">
         <v>124</v>
       </c>
@@ -20665,7 +20664,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="546" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="546" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A546">
         <v>127</v>
       </c>
@@ -20700,7 +20699,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="547" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="547" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A547">
         <v>128</v>
       </c>
@@ -20735,7 +20734,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="548" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="548" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A548">
         <v>130</v>
       </c>
@@ -20770,7 +20769,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="549" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="549" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A549">
         <v>131</v>
       </c>
@@ -20805,7 +20804,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="550" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="550" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A550">
         <v>132</v>
       </c>
@@ -20840,7 +20839,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="551" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="551" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A551">
         <v>133</v>
       </c>
@@ -20875,7 +20874,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="552" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="552" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A552">
         <v>134</v>
       </c>
@@ -20910,7 +20909,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="553" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="553" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A553">
         <v>137</v>
       </c>
@@ -20945,7 +20944,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="554" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="554" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A554">
         <v>138</v>
       </c>
@@ -20980,7 +20979,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="555" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="555" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A555">
         <v>115</v>
       </c>
@@ -21015,7 +21014,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="556" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="556" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A556">
         <v>115</v>
       </c>
@@ -21050,7 +21049,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="557" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="557" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A557">
         <v>107</v>
       </c>
@@ -21085,7 +21084,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="558" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="558" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A558">
         <v>47</v>
       </c>
@@ -21120,7 +21119,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="559" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="559" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A559">
         <v>3</v>
       </c>
@@ -21155,7 +21154,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="560" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="560" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A560">
         <v>4</v>
       </c>
@@ -21190,7 +21189,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="561" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="561" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A561">
         <v>12</v>
       </c>
@@ -21225,7 +21224,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="562" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="562" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A562">
         <v>16</v>
       </c>
@@ -21260,7 +21259,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="563" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="563" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A563">
         <v>21</v>
       </c>
@@ -21295,7 +21294,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="564" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="564" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A564">
         <v>25</v>
       </c>
@@ -21330,7 +21329,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="565" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="565" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A565">
         <v>27</v>
       </c>
@@ -21365,7 +21364,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="566" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="566" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A566">
         <v>28</v>
       </c>
@@ -21400,7 +21399,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="567" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="567" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A567">
         <v>30</v>
       </c>
@@ -21435,7 +21434,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="568" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="568" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A568">
         <v>30</v>
       </c>
@@ -21470,7 +21469,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="569" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="569" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A569">
         <v>32</v>
       </c>
@@ -21505,7 +21504,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="570" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="570" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A570">
         <v>34</v>
       </c>
@@ -21540,7 +21539,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="571" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="571" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A571">
         <v>38</v>
       </c>
@@ -21575,7 +21574,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="572" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="572" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A572">
         <v>43</v>
       </c>
@@ -21610,7 +21609,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="573" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="573" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A573">
         <v>49</v>
       </c>
@@ -21645,7 +21644,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="574" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="574" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A574">
         <v>50</v>
       </c>
@@ -21680,7 +21679,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="575" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="575" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A575">
         <v>51</v>
       </c>
@@ -21715,7 +21714,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="576" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="576" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A576">
         <v>52</v>
       </c>
@@ -21750,7 +21749,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="577" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="577" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A577">
         <v>53</v>
       </c>
@@ -21785,7 +21784,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="578" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="578" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A578">
         <v>54</v>
       </c>
@@ -21820,7 +21819,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="579" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="579" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A579">
         <v>56</v>
       </c>
@@ -21855,7 +21854,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="580" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="580" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A580">
         <v>57</v>
       </c>
@@ -21890,7 +21889,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="581" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="581" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A581">
         <v>61</v>
       </c>
@@ -21925,7 +21924,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="582" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="582" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A582">
         <v>64</v>
       </c>
@@ -21960,7 +21959,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="583" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="583" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A583">
         <v>65</v>
       </c>
@@ -21995,7 +21994,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="584" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="584" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A584">
         <v>67</v>
       </c>
@@ -22030,7 +22029,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="585" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="585" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A585">
         <v>71</v>
       </c>
@@ -22065,7 +22064,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="586" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="586" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A586">
         <v>71</v>
       </c>
@@ -22100,7 +22099,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="587" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="587" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A587">
         <v>75</v>
       </c>
@@ -22135,7 +22134,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="588" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="588" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A588">
         <v>78</v>
       </c>
@@ -22170,7 +22169,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="589" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="589" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A589">
         <v>79</v>
       </c>
@@ -22205,7 +22204,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="590" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="590" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A590">
         <v>83</v>
       </c>
@@ -22240,7 +22239,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="591" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="591" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A591">
         <v>85</v>
       </c>
@@ -22275,7 +22274,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="592" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="592" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A592">
         <v>88</v>
       </c>
@@ -22310,7 +22309,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="593" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="593" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A593">
         <v>89</v>
       </c>
@@ -22345,7 +22344,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="594" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="594" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A594">
         <v>91</v>
       </c>
@@ -22380,7 +22379,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="595" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="595" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A595">
         <v>96</v>
       </c>
@@ -22415,7 +22414,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="596" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="596" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A596">
         <v>96</v>
       </c>
@@ -22450,7 +22449,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="597" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="597" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A597">
         <v>101</v>
       </c>
@@ -22485,7 +22484,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="598" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="598" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A598">
         <v>105</v>
       </c>
@@ -22520,7 +22519,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="599" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="599" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A599">
         <v>113</v>
       </c>
@@ -22555,7 +22554,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="600" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="600" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A600">
         <v>121</v>
       </c>
@@ -22590,7 +22589,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="601" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="601" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A601">
         <v>124</v>
       </c>
@@ -22625,7 +22624,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="602" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="602" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A602">
         <v>127</v>
       </c>
@@ -22660,7 +22659,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="603" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="603" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A603">
         <v>128</v>
       </c>
@@ -22695,7 +22694,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="604" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="604" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A604">
         <v>130</v>
       </c>
@@ -22730,7 +22729,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="605" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="605" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A605">
         <v>131</v>
       </c>
@@ -22765,7 +22764,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="606" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="606" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A606">
         <v>132</v>
       </c>
@@ -22800,7 +22799,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="607" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="607" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A607">
         <v>133</v>
       </c>
@@ -22835,7 +22834,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="608" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="608" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A608">
         <v>134</v>
       </c>
@@ -22870,7 +22869,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="609" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="609" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A609">
         <v>137</v>
       </c>
@@ -22905,7 +22904,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="610" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="610" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A610">
         <v>138</v>
       </c>
@@ -22940,7 +22939,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="611" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="611" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A611">
         <v>115</v>
       </c>
@@ -22975,7 +22974,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="612" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="612" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A612">
         <v>107</v>
       </c>
@@ -23010,7 +23009,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="613" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="613" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A613">
         <v>110</v>
       </c>
@@ -23045,7 +23044,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="614" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="614" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A614">
         <v>3</v>
       </c>
@@ -23080,7 +23079,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="615" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="615" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A615">
         <v>4</v>
       </c>
@@ -23115,7 +23114,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="616" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="616" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A616">
         <v>12</v>
       </c>
@@ -23150,7 +23149,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="617" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="617" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A617">
         <v>16</v>
       </c>
@@ -23185,7 +23184,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="618" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="618" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A618">
         <v>21</v>
       </c>
@@ -23220,7 +23219,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="619" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="619" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A619">
         <v>25</v>
       </c>
@@ -23255,7 +23254,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="620" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="620" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A620">
         <v>27</v>
       </c>
@@ -23290,7 +23289,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="621" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="621" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A621">
         <v>28</v>
       </c>
@@ -23325,7 +23324,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="622" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="622" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A622">
         <v>30</v>
       </c>
@@ -23360,7 +23359,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="623" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="623" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A623">
         <v>30</v>
       </c>
@@ -23395,7 +23394,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="624" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="624" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A624">
         <v>32</v>
       </c>
@@ -23430,7 +23429,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="625" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="625" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A625">
         <v>34</v>
       </c>
@@ -23465,7 +23464,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="626" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="626" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A626">
         <v>38</v>
       </c>
@@ -23500,7 +23499,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="627" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="627" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A627">
         <v>43</v>
       </c>
@@ -23535,7 +23534,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="628" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="628" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A628">
         <v>49</v>
       </c>
@@ -23570,7 +23569,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="629" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="629" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A629">
         <v>50</v>
       </c>
@@ -23605,7 +23604,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="630" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="630" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A630">
         <v>51</v>
       </c>
@@ -23640,7 +23639,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="631" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="631" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A631">
         <v>52</v>
       </c>
@@ -23675,7 +23674,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="632" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="632" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A632">
         <v>53</v>
       </c>
@@ -23710,7 +23709,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="633" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="633" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A633">
         <v>54</v>
       </c>
@@ -23745,7 +23744,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="634" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="634" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A634">
         <v>56</v>
       </c>
@@ -23780,7 +23779,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="635" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="635" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A635">
         <v>57</v>
       </c>
@@ -23815,7 +23814,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="636" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="636" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A636">
         <v>61</v>
       </c>
@@ -23850,7 +23849,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="637" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="637" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A637">
         <v>64</v>
       </c>
@@ -23885,7 +23884,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="638" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="638" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A638">
         <v>65</v>
       </c>
@@ -23920,7 +23919,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="639" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="639" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A639">
         <v>67</v>
       </c>
@@ -23955,7 +23954,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="640" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="640" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A640">
         <v>71</v>
       </c>
@@ -23990,7 +23989,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="641" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="641" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A641">
         <v>71</v>
       </c>
@@ -24025,7 +24024,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="642" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="642" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A642">
         <v>75</v>
       </c>
@@ -24060,7 +24059,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="643" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="643" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A643">
         <v>78</v>
       </c>
@@ -24095,7 +24094,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="644" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="644" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A644">
         <v>79</v>
       </c>
@@ -24130,7 +24129,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="645" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="645" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A645">
         <v>83</v>
       </c>
@@ -24165,7 +24164,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="646" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="646" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A646">
         <v>85</v>
       </c>
@@ -24200,7 +24199,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="647" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="647" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A647">
         <v>88</v>
       </c>
@@ -24235,7 +24234,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="648" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="648" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A648">
         <v>89</v>
       </c>
@@ -24270,7 +24269,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="649" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="649" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A649">
         <v>91</v>
       </c>
@@ -24305,7 +24304,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="650" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="650" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A650">
         <v>96</v>
       </c>
@@ -24340,7 +24339,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="651" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="651" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A651">
         <v>96</v>
       </c>
@@ -24375,7 +24374,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="652" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="652" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A652">
         <v>101</v>
       </c>
@@ -24410,7 +24409,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="653" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="653" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A653">
         <v>105</v>
       </c>
@@ -24445,7 +24444,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="654" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="654" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A654">
         <v>113</v>
       </c>
@@ -24480,7 +24479,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="655" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="655" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A655">
         <v>121</v>
       </c>
@@ -24515,7 +24514,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="656" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="656" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A656">
         <v>124</v>
       </c>
@@ -24550,7 +24549,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="657" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="657" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A657">
         <v>127</v>
       </c>
@@ -24585,7 +24584,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="658" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="658" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A658">
         <v>128</v>
       </c>
@@ -24620,7 +24619,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="659" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="659" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A659">
         <v>130</v>
       </c>
@@ -24655,7 +24654,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="660" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="660" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A660">
         <v>131</v>
       </c>
@@ -24690,7 +24689,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="661" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="661" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A661">
         <v>132</v>
       </c>
@@ -24725,7 +24724,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="662" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="662" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A662">
         <v>133</v>
       </c>
@@ -24760,7 +24759,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="663" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="663" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A663">
         <v>134</v>
       </c>
@@ -24795,7 +24794,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="664" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="664" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A664">
         <v>137</v>
       </c>
@@ -24830,7 +24829,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="665" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="665" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A665">
         <v>138</v>
       </c>
@@ -24865,7 +24864,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="666" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="666" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A666">
         <v>115</v>
       </c>
@@ -24900,7 +24899,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="667" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="667" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A667">
         <v>3</v>
       </c>
@@ -24935,7 +24934,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="668" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="668" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A668">
         <v>4</v>
       </c>
@@ -24970,7 +24969,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="669" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="669" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A669">
         <v>12</v>
       </c>
@@ -25005,7 +25004,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="670" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="670" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A670">
         <v>16</v>
       </c>
@@ -25040,7 +25039,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="671" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="671" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A671">
         <v>21</v>
       </c>
@@ -25075,7 +25074,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="672" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="672" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A672">
         <v>25</v>
       </c>
@@ -25110,7 +25109,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="673" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="673" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A673">
         <v>27</v>
       </c>
@@ -25145,7 +25144,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="674" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="674" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A674">
         <v>28</v>
       </c>
@@ -25180,7 +25179,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="675" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="675" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A675">
         <v>30</v>
       </c>
@@ -25215,7 +25214,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="676" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="676" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A676">
         <v>30</v>
       </c>
@@ -25250,7 +25249,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="677" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="677" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A677">
         <v>32</v>
       </c>
@@ -25285,7 +25284,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="678" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="678" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A678">
         <v>34</v>
       </c>
@@ -25320,7 +25319,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="679" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="679" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A679">
         <v>38</v>
       </c>
@@ -25355,7 +25354,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="680" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="680" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A680">
         <v>43</v>
       </c>
@@ -25390,7 +25389,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="681" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="681" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A681">
         <v>49</v>
       </c>
@@ -25425,7 +25424,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="682" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="682" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A682">
         <v>50</v>
       </c>
@@ -25460,7 +25459,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="683" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="683" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A683">
         <v>51</v>
       </c>
@@ -25495,7 +25494,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="684" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="684" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A684">
         <v>52</v>
       </c>
@@ -25530,7 +25529,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="685" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="685" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A685">
         <v>53</v>
       </c>
@@ -25565,7 +25564,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="686" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="686" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A686">
         <v>54</v>
       </c>
@@ -25600,7 +25599,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="687" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="687" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A687">
         <v>56</v>
       </c>
@@ -25635,7 +25634,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="688" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="688" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A688">
         <v>57</v>
       </c>
@@ -25670,7 +25669,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="689" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="689" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A689">
         <v>61</v>
       </c>
@@ -25705,7 +25704,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="690" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="690" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A690">
         <v>64</v>
       </c>
@@ -25740,7 +25739,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="691" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="691" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A691">
         <v>65</v>
       </c>
@@ -25775,7 +25774,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="692" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="692" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A692">
         <v>67</v>
       </c>
@@ -25810,7 +25809,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="693" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="693" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A693">
         <v>71</v>
       </c>
@@ -25845,7 +25844,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="694" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="694" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A694">
         <v>71</v>
       </c>
@@ -25880,7 +25879,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="695" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="695" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A695">
         <v>75</v>
       </c>
@@ -25915,7 +25914,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="696" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="696" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A696">
         <v>78</v>
       </c>
@@ -25950,7 +25949,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="697" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="697" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A697">
         <v>79</v>
       </c>
@@ -25985,7 +25984,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="698" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="698" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A698">
         <v>83</v>
       </c>
@@ -26020,7 +26019,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="699" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="699" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A699">
         <v>85</v>
       </c>
@@ -26055,7 +26054,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="700" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="700" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A700">
         <v>88</v>
       </c>
@@ -26090,7 +26089,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="701" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="701" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A701">
         <v>89</v>
       </c>
@@ -26125,7 +26124,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="702" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="702" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A702">
         <v>91</v>
       </c>
@@ -26160,7 +26159,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="703" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="703" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A703">
         <v>96</v>
       </c>
@@ -26195,7 +26194,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="704" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="704" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A704">
         <v>96</v>
       </c>
@@ -26230,7 +26229,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="705" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="705" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A705">
         <v>101</v>
       </c>
@@ -26265,7 +26264,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="706" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="706" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A706">
         <v>105</v>
       </c>
@@ -26300,7 +26299,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="707" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="707" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A707">
         <v>113</v>
       </c>
@@ -26335,7 +26334,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="708" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="708" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A708">
         <v>121</v>
       </c>
@@ -26370,7 +26369,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="709" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="709" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A709">
         <v>124</v>
       </c>
@@ -26405,7 +26404,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="710" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="710" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A710">
         <v>127</v>
       </c>
@@ -26440,7 +26439,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="711" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="711" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A711">
         <v>128</v>
       </c>
@@ -26475,7 +26474,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="712" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="712" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A712">
         <v>130</v>
       </c>
@@ -26510,7 +26509,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="713" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="713" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A713">
         <v>131</v>
       </c>
@@ -26545,7 +26544,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="714" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="714" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A714">
         <v>132</v>
       </c>
@@ -26580,7 +26579,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="715" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="715" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A715">
         <v>133</v>
       </c>
@@ -26615,7 +26614,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="716" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="716" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A716">
         <v>134</v>
       </c>
@@ -26650,7 +26649,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="717" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="717" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A717">
         <v>137</v>
       </c>
@@ -26685,7 +26684,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="718" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="718" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A718">
         <v>138</v>
       </c>
@@ -26720,7 +26719,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="719" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="719" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A719">
         <v>115</v>
       </c>
@@ -26755,7 +26754,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="720" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="720" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A720">
         <v>115</v>
       </c>
@@ -26790,7 +26789,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="721" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="721" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A721">
         <v>115</v>
       </c>
@@ -26825,7 +26824,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="722" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="722" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A722">
         <v>115</v>
       </c>
@@ -26860,7 +26859,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="723" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="723" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A723">
         <v>21</v>
       </c>
@@ -26895,7 +26894,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="724" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="724" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A724">
         <v>51</v>
       </c>
@@ -26930,7 +26929,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="725" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="725" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A725">
         <v>56</v>
       </c>
@@ -26965,7 +26964,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="726" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="726" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A726">
         <v>137</v>
       </c>
@@ -27000,7 +26999,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="727" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="727" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A727">
         <v>66</v>
       </c>
@@ -27035,7 +27034,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="728" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="728" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A728">
         <v>21</v>
       </c>
@@ -27070,7 +27069,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="729" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="729" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A729">
         <v>51</v>
       </c>
@@ -27105,7 +27104,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="730" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="730" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A730">
         <v>53</v>
       </c>
@@ -27140,7 +27139,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="731" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="731" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A731">
         <v>128</v>
       </c>
@@ -27175,7 +27174,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="732" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="732" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A732">
         <v>137</v>
       </c>
@@ -27210,7 +27209,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="733" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="733" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A733">
         <v>65</v>
       </c>
@@ -27245,7 +27244,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="734" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="734" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A734">
         <v>66</v>
       </c>
@@ -27280,7 +27279,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="735" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="735" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A735">
         <v>105</v>
       </c>
@@ -27315,7 +27314,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="736" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="736" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A736">
         <v>37</v>
       </c>
@@ -27350,7 +27349,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="737" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="737" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A737">
         <v>19</v>
       </c>
@@ -27385,7 +27384,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="738" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="738" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A738">
         <v>115</v>
       </c>
@@ -27420,7 +27419,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="739" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="739" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A739">
         <v>19</v>
       </c>
@@ -27455,7 +27454,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="740" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="740" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A740">
         <v>4</v>
       </c>
@@ -27490,7 +27489,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="741" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="741" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A741">
         <v>12</v>
       </c>
@@ -27525,7 +27524,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="742" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="742" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A742">
         <v>39</v>
       </c>
@@ -27560,7 +27559,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="743" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="743" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A743">
         <v>117</v>
       </c>
@@ -27595,7 +27594,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="744" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="744" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A744">
         <v>20</v>
       </c>
@@ -27630,7 +27629,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="745" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="745" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A745">
         <v>20</v>
       </c>
@@ -27665,7 +27664,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="746" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="746" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A746">
         <v>20</v>
       </c>
@@ -27700,7 +27699,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="747" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="747" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A747">
         <v>20</v>
       </c>
@@ -27735,7 +27734,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="748" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="748" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A748">
         <v>127</v>
       </c>
@@ -27770,7 +27769,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="749" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="749" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A749">
         <v>127</v>
       </c>
@@ -27805,7 +27804,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="750" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="750" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A750">
         <v>127</v>
       </c>
@@ -27840,7 +27839,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="751" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="751" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A751">
         <v>127</v>
       </c>
@@ -27875,7 +27874,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="752" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="752" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A752">
         <v>127</v>
       </c>
@@ -27910,7 +27909,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="753" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="753" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A753">
         <v>127</v>
       </c>
@@ -27945,7 +27944,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="754" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="754" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A754">
         <v>20</v>
       </c>
@@ -27980,7 +27979,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="755" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="755" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A755">
         <v>20</v>
       </c>
@@ -28015,7 +28014,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="756" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="756" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A756">
         <v>20</v>
       </c>
@@ -28050,7 +28049,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="757" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="757" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A757">
         <v>20</v>
       </c>
@@ -28085,7 +28084,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="758" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="758" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A758">
         <v>127</v>
       </c>
@@ -28120,7 +28119,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="759" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="759" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A759">
         <v>103</v>
       </c>
@@ -28155,7 +28154,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="760" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="760" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A760">
         <v>103</v>
       </c>
@@ -28190,7 +28189,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="761" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="761" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A761">
         <v>136</v>
       </c>
@@ -28225,7 +28224,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="762" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="762" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A762">
         <v>15</v>
       </c>
@@ -28260,7 +28259,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="763" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="763" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A763">
         <v>47</v>
       </c>
@@ -28295,7 +28294,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="764" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="764" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A764">
         <v>30</v>
       </c>
@@ -28330,7 +28329,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="765" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="765" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A765">
         <v>30</v>
       </c>
@@ -28365,7 +28364,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="766" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="766" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A766">
         <v>47</v>
       </c>
@@ -28400,7 +28399,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="767" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="767" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A767">
         <v>30</v>
       </c>
@@ -28435,7 +28434,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="768" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="768" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A768">
         <v>18</v>
       </c>
@@ -28470,7 +28469,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="769" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="769" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A769">
         <v>18</v>
       </c>
@@ -28505,7 +28504,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="770" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="770" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A770">
         <v>122</v>
       </c>
@@ -28540,7 +28539,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="771" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="771" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A771">
         <v>122</v>
       </c>
@@ -28575,7 +28574,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="772" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="772" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A772">
         <v>122</v>
       </c>
@@ -28610,7 +28609,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="773" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="773" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A773">
         <v>122</v>
       </c>
@@ -28645,7 +28644,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="774" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="774" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A774">
         <v>122</v>
       </c>
@@ -28680,7 +28679,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="775" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="775" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A775">
         <v>18</v>
       </c>
@@ -28715,7 +28714,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="776" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="776" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A776">
         <v>18</v>
       </c>
@@ -28750,7 +28749,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="777" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="777" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A777">
         <v>84</v>
       </c>
@@ -28785,7 +28784,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="778" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="778" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A778">
         <v>132</v>
       </c>
@@ -28820,7 +28819,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="779" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="779" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A779">
         <v>81</v>
       </c>
@@ -28855,7 +28854,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="780" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="780" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A780">
         <v>105</v>
       </c>
@@ -28890,7 +28889,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="781" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="781" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A781">
         <v>117</v>
       </c>
@@ -28925,7 +28924,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="782" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="782" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A782">
         <v>100</v>
       </c>
@@ -28960,7 +28959,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="783" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="783" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A783">
         <v>135</v>
       </c>
@@ -28995,7 +28994,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="784" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="784" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A784">
         <v>100</v>
       </c>
@@ -29030,7 +29029,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="785" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="785" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A785">
         <v>135</v>
       </c>
@@ -29065,7 +29064,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="786" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="786" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A786">
         <v>100</v>
       </c>
@@ -29100,7 +29099,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="787" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="787" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A787">
         <v>135</v>
       </c>
@@ -29135,7 +29134,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="788" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="788" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A788">
         <v>100</v>
       </c>
@@ -29170,7 +29169,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="789" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="789" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A789">
         <v>135</v>
       </c>
@@ -29205,7 +29204,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="790" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="790" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A790">
         <v>100</v>
       </c>
@@ -29240,7 +29239,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="791" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="791" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A791">
         <v>135</v>
       </c>
@@ -29275,7 +29274,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="792" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="792" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A792">
         <v>100</v>
       </c>
@@ -29310,7 +29309,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="793" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="793" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A793">
         <v>135</v>
       </c>
@@ -29345,7 +29344,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="794" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="794" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A794">
         <v>127</v>
       </c>
@@ -29380,7 +29379,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="795" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="795" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A795">
         <v>136</v>
       </c>
@@ -29415,7 +29414,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="796" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="796" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A796">
         <v>47</v>
       </c>
@@ -29450,7 +29449,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="797" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="797" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A797">
         <v>47</v>
       </c>
@@ -29485,7 +29484,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="798" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="798" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A798">
         <v>18</v>
       </c>
@@ -29520,7 +29519,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="799" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="799" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A799">
         <v>74</v>
       </c>
@@ -29555,7 +29554,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="800" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="800" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A800">
         <v>19</v>
       </c>
@@ -29590,7 +29589,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="801" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="801" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A801">
         <v>35</v>
       </c>
@@ -29625,7 +29624,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="802" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="802" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A802">
         <v>43</v>
       </c>
@@ -29660,7 +29659,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="803" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="803" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A803">
         <v>57</v>
       </c>
@@ -29695,7 +29694,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="804" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="804" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A804">
         <v>61</v>
       </c>
@@ -29730,7 +29729,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="805" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="805" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A805">
         <v>71</v>
       </c>
@@ -29765,7 +29764,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="806" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="806" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A806">
         <v>71</v>
       </c>
@@ -29800,7 +29799,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="807" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="807" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A807">
         <v>18</v>
       </c>
@@ -29836,13 +29835,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K807" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="2005"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:K807" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K807">
     <sortCondition ref="E2:E807"/>
   </sortState>
